--- a/eval_output/BASE_CIFAR_noniid1000.xlsx
+++ b/eval_output/BASE_CIFAR_noniid1000.xlsx
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>102806513520.2546</v>
+        <v>102860609073.7104</v>
       </c>
       <c r="D2" t="n">
         <v>528559936</v>
@@ -503,7 +503,7 @@
         <v>2116781952</v>
       </c>
       <c r="F2" t="n">
-        <v>62.53768418362176</v>
+        <v>62.57059076241638</v>
       </c>
       <c r="G2" t="n">
         <v>476754112</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>102981898091.1495</v>
+        <v>103067177033.5702</v>
       </c>
       <c r="D3" t="n">
         <v>528512896</v>
@@ -536,7 +536,7 @@
         <v>2118147072</v>
       </c>
       <c r="F3" t="n">
-        <v>62.64437144038924</v>
+        <v>62.69624702089482</v>
       </c>
       <c r="G3" t="n">
         <v>476754112</v>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>103249998555.5057</v>
+        <v>103254306065.2689</v>
       </c>
       <c r="D5" t="n">
         <v>476754112</v>
@@ -602,7 +602,7 @@
         <v>2117831936</v>
       </c>
       <c r="F5" t="n">
-        <v>62.80745820984854</v>
+        <v>62.81007848823325</v>
       </c>
       <c r="G5" t="n">
         <v>476754112</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>103883818861.0559</v>
+        <v>103929610283.8072</v>
       </c>
       <c r="D6" t="n">
         <v>476754112</v>
@@ -635,7 +635,7 @@
         <v>2117464448</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>63.19301407338681</v>
+        <v>63.22086921053995</v>
       </c>
       <c r="G6" t="n">
         <v>476754112</v>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>104275611368.6182</v>
+        <v>104306892465.8012</v>
       </c>
       <c r="D8" t="n">
         <v>528418784</v>
@@ -701,7 +701,7 @@
         <v>2119354624</v>
       </c>
       <c r="F8" t="n">
-        <v>63.43134329265963</v>
+        <v>63.45037173073775</v>
       </c>
       <c r="G8" t="n">
         <v>476754112</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103870537195.6473</v>
+        <v>103969008375.145</v>
       </c>
       <c r="D9" t="n">
         <v>528559936</v>
@@ -734,7 +734,7 @@
         <v>2120667136</v>
       </c>
       <c r="F9" t="n">
-        <v>63.18493477404758</v>
+        <v>63.244835254219</v>
       </c>
       <c r="G9" t="n">
         <v>476754112</v>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>104142928585.8308</v>
+        <v>104173359647.8606</v>
       </c>
       <c r="D10" t="n">
         <v>502855808</v>
@@ -767,7 +767,7 @@
         <v>2117517056</v>
       </c>
       <c r="F10" t="n">
-        <v>63.35063173380562</v>
+        <v>63.36914309151466</v>
       </c>
       <c r="G10" t="n">
         <v>476754112</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>104606583386.8198</v>
+        <v>104665049706.9255</v>
       </c>
       <c r="D11" t="n">
         <v>476796000</v>
@@ -800,7 +800,7 @@
         <v>2118252032</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>63.63267512309688</v>
+        <v>63.66824045973704</v>
       </c>
       <c r="G11" t="n">
         <v>476754112</v>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>104865759047.6118</v>
+        <v>105019293769.6846</v>
       </c>
       <c r="D12" t="n">
         <v>476796000</v>
@@ -833,7 +833,7 @@
         <v>2115994496</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>63.79033289270408</v>
+        <v>63.88372878398985</v>
       </c>
       <c r="G12" t="n">
         <v>476754112</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>67199940718.9443</v>
+        <v>67270395023.346</v>
       </c>
       <c r="D2" t="n">
         <v>528559904</v>
@@ -960,7 +960,7 @@
         <v>1595316736</v>
       </c>
       <c r="F2" t="n">
-        <v>60.07479855306028</v>
+        <v>60.13778265838606</v>
       </c>
       <c r="G2" t="n">
         <v>476712224</v>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>67131787360.56126</v>
+        <v>67224078918.94093</v>
       </c>
       <c r="D3" t="n">
         <v>528465824</v>
@@ -993,7 +993,7 @@
         <v>1594949248</v>
       </c>
       <c r="F3" t="n">
-        <v>60.01387142675968</v>
+        <v>60.09637740397468</v>
       </c>
       <c r="G3" t="n">
         <v>476712224</v>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>67291340336.383</v>
+        <v>67367105017.85156</v>
       </c>
       <c r="D4" t="n">
         <v>503122688</v>
@@ -1026,7 +1026,7 @@
         <v>1594844160</v>
       </c>
       <c r="F4" t="n">
-        <v>60.15650716093572</v>
+        <v>60.22423858938588</v>
       </c>
       <c r="G4" t="n">
         <v>476712224</v>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67325335456.63178</v>
+        <v>67457731091.62306</v>
       </c>
       <c r="D5" t="n">
         <v>476712224</v>
@@ -1059,7 +1059,7 @@
         <v>1591798912</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>60.18689781275599</v>
+        <v>60.30525567165159</v>
       </c>
       <c r="G5" t="n">
         <v>476712224</v>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67783535629.51659</v>
+        <v>67892805966.36538</v>
       </c>
       <c r="D6" t="n">
         <v>476712224</v>
@@ -1092,7 +1092,7 @@
         <v>1595106688</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>60.59651548188695</v>
+        <v>60.69419999475684</v>
       </c>
       <c r="G6" t="n">
         <v>476712224</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>67813089286.39359</v>
+        <v>67901378901.83753</v>
       </c>
       <c r="D8" t="n">
         <v>528418784</v>
@@ -1158,7 +1158,7 @@
         <v>1593846656</v>
       </c>
       <c r="F8" t="n">
-        <v>60.62293559423225</v>
+        <v>60.70186395049829</v>
       </c>
       <c r="G8" t="n">
         <v>476712224</v>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>67370735450.66628</v>
+        <v>67478291346.33538</v>
       </c>
       <c r="D9" t="n">
         <v>528512864</v>
@@ -1191,7 +1191,7 @@
         <v>1593846656</v>
       </c>
       <c r="F9" t="n">
-        <v>60.22748409105851</v>
+        <v>60.32363594322368</v>
       </c>
       <c r="G9" t="n">
         <v>476712224</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>67920695933.82513</v>
+        <v>68010941369.31241</v>
       </c>
       <c r="D10" t="n">
         <v>502811360</v>
@@ -1224,7 +1224,7 @@
         <v>1594319104</v>
       </c>
       <c r="F10" t="n">
-        <v>60.71913281700149</v>
+        <v>60.79980961967764</v>
       </c>
       <c r="G10" t="n">
         <v>476712224</v>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>68293549729.67438</v>
+        <v>68466658853.09698</v>
       </c>
       <c r="D11" t="n">
         <v>476754112</v>
@@ -1257,7 +1257,7 @@
         <v>1594844160</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>61.05245329966484</v>
+        <v>61.20720783673808</v>
       </c>
       <c r="G11" t="n">
         <v>476712224</v>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>68521559227.4871</v>
+        <v>68679680624.35915</v>
       </c>
       <c r="D12" t="n">
         <v>476796000</v>
@@ -1290,7 +1290,7 @@
         <v>1592323968</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>61.25628717961679</v>
+        <v>61.39764312372016</v>
       </c>
       <c r="G12" t="n">
         <v>476712224</v>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30480626283.03356</v>
+        <v>30637403418.68931</v>
       </c>
       <c r="D2" t="n">
         <v>528465792</v>
@@ -1417,7 +1417,7 @@
         <v>1074796544</v>
       </c>
       <c r="F2" t="n">
-        <v>50.83524847144077</v>
+        <v>51.0967196292738</v>
       </c>
       <c r="G2" t="n">
         <v>476670336</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30618017656.8662</v>
+        <v>30673685764.44249</v>
       </c>
       <c r="D3" t="n">
         <v>528418784</v>
@@ -1450,7 +1450,7 @@
         <v>1076266624</v>
       </c>
       <c r="F3" t="n">
-        <v>51.06438827197375</v>
+        <v>51.15723092075328</v>
       </c>
       <c r="G3" t="n">
         <v>476670336</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30858211776.41825</v>
+        <v>31051317356.60803</v>
       </c>
       <c r="D4" t="n">
         <v>502811392</v>
@@ -1482,8 +1482,8 @@
       <c r="E4" t="n">
         <v>1074586496</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>51.46498134494497</v>
+      <c r="F4" t="n">
+        <v>51.78704067728989</v>
       </c>
       <c r="G4" t="n">
         <v>476670336</v>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30763853282.74302</v>
+        <v>31237493026.64675</v>
       </c>
       <c r="D5" t="n">
         <v>476670336</v>
@@ -1515,8 +1515,8 @@
       <c r="E5" t="n">
         <v>1073904000</v>
       </c>
-      <c r="F5" t="n">
-        <v>51.30761130186153</v>
+      <c r="F5" s="3" t="n">
+        <v>52.09754238279533</v>
       </c>
       <c r="G5" t="n">
         <v>476670336</v>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31167826919.21631</v>
+        <v>31333770880.96713</v>
       </c>
       <c r="D6" t="n">
         <v>476670336</v>
@@ -1549,7 +1549,7 @@
         <v>1073746560</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>51.98135402602144</v>
+        <v>52.25811351415025</v>
       </c>
       <c r="G6" t="n">
         <v>476670336</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30900415181.58642</v>
+        <v>31041194829.72603</v>
       </c>
       <c r="D8" t="n">
         <v>528418784</v>
@@ -1615,7 +1615,7 @@
         <v>1071803776</v>
       </c>
       <c r="F8" t="n">
-        <v>51.53536771326112</v>
+        <v>51.77015843988352</v>
       </c>
       <c r="G8" t="n">
         <v>476670336</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30913279647.0662</v>
+        <v>30988026510.91449</v>
       </c>
       <c r="D9" t="n">
         <v>528465792</v>
@@ -1648,7 +1648,7 @@
         <v>1072958912</v>
       </c>
       <c r="F9" t="n">
-        <v>51.55682292527167</v>
+        <v>51.68148491091807</v>
       </c>
       <c r="G9" t="n">
         <v>476670336</v>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30948190736.86025</v>
+        <v>31123701216.61319</v>
       </c>
       <c r="D10" t="n">
         <v>502677984</v>
@@ -1681,7 +1681,7 @@
         <v>1073431424</v>
       </c>
       <c r="F10" t="n">
-        <v>51.61504725136032</v>
+        <v>51.90776167148852</v>
       </c>
       <c r="G10" t="n">
         <v>476670336</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30994574983.1368</v>
+        <v>31371545705.48095</v>
       </c>
       <c r="D11" t="n">
         <v>476712256</v>
@@ -1713,8 +1713,8 @@
       <c r="E11" t="n">
         <v>1070806208</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>51.69240637983536</v>
+      <c r="F11" s="2" t="n">
+        <v>52.32111394505657</v>
       </c>
       <c r="G11" t="n">
         <v>476670336</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>31163058433.70331</v>
+        <v>31281375544.21888</v>
       </c>
       <c r="D12" t="n">
         <v>476754112</v>
@@ -1746,8 +1746,8 @@
       <c r="E12" t="n">
         <v>1071068800</v>
       </c>
-      <c r="F12" s="2" t="n">
-        <v>51.97340119908032</v>
+      <c r="F12" s="3" t="n">
+        <v>52.17072915604653</v>
       </c>
       <c r="G12" t="n">
         <v>476670336</v>
